--- a/ｱｲﾑﾚﾃﾞｨスケジュール.xlsx
+++ b/ｱｲﾑﾚﾃﾞｨスケジュール.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1810B24-1C9D-4128-BC18-A494B62FB65D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CAA8DD-481D-48ED-99BF-C53625617B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="480" windowWidth="26850" windowHeight="11295" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="165" yWindow="-15075" windowWidth="26850" windowHeight="14655" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -126,20 +126,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ﾁｭｰﾄﾘｱﾙｼｰﾝ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>手直し期間</t>
-    <rPh sb="0" eb="2">
-      <t>テナオ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>キカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>最終確認</t>
     <rPh sb="0" eb="2">
       <t>サイシュウ</t>
@@ -194,10 +180,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>デバッグ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t xml:space="preserve"> シーン作成(ﾀｲﾄﾙ､ｾﾚｸﾄ)など</t>
     <rPh sb="4" eb="6">
       <t>サクセイ</t>
@@ -214,6 +196,24 @@
   </si>
   <si>
     <t>ステージギミック</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エネミー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブラッシュアップ（マップ）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ブラッシュアップ（追加要素）</t>
+    <rPh sb="9" eb="11">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨウソ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1055,18 +1055,18 @@
         <v>6</v>
       </c>
       <c r="R3" s="16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="S3" s="23"/>
       <c r="T3" s="23"/>
       <c r="U3" s="23" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
       <c r="Y3" s="22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z3" s="22"/>
       <c r="AA3" s="22"/>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="AF3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AG3" s="16"/>
       <c r="AH3" s="16"/>
@@ -1085,11 +1085,11 @@
       <c r="AJ3" s="9"/>
       <c r="AK3" s="9"/>
       <c r="AL3" s="14" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AM3" s="14"/>
       <c r="AN3" s="19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO3" s="19"/>
       <c r="AP3" s="19"/>
@@ -1132,7 +1132,7 @@
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R4" s="11"/>
       <c r="S4" s="12"/>
@@ -1155,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="AF4" s="21" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AG4" s="21"/>
       <c r="AH4" s="21"/>
@@ -1165,12 +1165,12 @@
       <c r="AJ4" s="9"/>
       <c r="AK4" s="9"/>
       <c r="AL4" s="17" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AM4" s="17"/>
       <c r="AN4" s="19"/>
       <c r="AO4" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP4" s="19"/>
       <c r="AQ4" s="9"/>
@@ -1212,7 +1212,7 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="R5" s="24"/>
       <c r="S5" s="24"/>
@@ -1222,10 +1222,10 @@
       <c r="W5" s="9"/>
       <c r="X5" s="9"/>
       <c r="Y5" s="18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z5" s="24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AA5" s="24"/>
       <c r="AB5" s="15" t="s">
@@ -1237,7 +1237,7 @@
         <v>9</v>
       </c>
       <c r="AF5" s="18" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AG5" s="26"/>
       <c r="AH5" s="18"/>
@@ -1245,11 +1245,11 @@
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9"/>
       <c r="AL5" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AM5" s="24"/>
       <c r="AN5" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO5" s="19"/>
       <c r="AP5" s="19"/>
@@ -1291,17 +1291,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1496,6 +1485,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1506,17 +1506,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1535,6 +1524,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>

--- a/ｱｲﾑﾚﾃﾞｨスケジュール.xlsx
+++ b/ｱｲﾑﾚﾃﾞｨスケジュール.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\チーム制作\新しいフォルダー\GameProbuctionPractice1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9CAA8DD-481D-48ED-99BF-C53625617B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7341ADEE-6BB1-4A21-8D7A-CE5401AE0AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="-15075" windowWidth="26850" windowHeight="14655" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
+    <workbookView xWindow="795" yWindow="-15630" windowWidth="26850" windowHeight="14655" xr2:uid="{A0BA4298-C2C7-4C54-BB3A-0BA7CD3DD91A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -815,6 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1593A4E0-6E65-4532-B1F4-86DE2F579452}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:BH6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
@@ -1291,6 +1292,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101005F0D9E193D28814892BA96752E68B42F" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7ef2c4f7c5cf37d6221d7b1dda883374">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c" xmlns:ns3="26553de7-2a3a-444c-a024-df4cb947fd03" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="725cefcd41332f88909580cd13155635" ns2:_="" ns3:_="">
     <xsd:import namespace="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
@@ -1485,17 +1497,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="26553de7-2a3a-444c-a024-df4cb947fd03" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1506,6 +1507,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
+    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974AEB67-0EB4-422A-8375-3AEC86DF31AC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1524,17 +1536,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4AC433-DB2B-4AE9-979C-606A42CB94A1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="26553de7-2a3a-444c-a024-df4cb947fd03"/>
-    <ds:schemaRef ds:uri="c0d4a769-b4b6-44f5-bafd-bfbeb89b0b0c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDC1435B-6AB6-4AB2-8181-7AB2A8D90409}">
   <ds:schemaRefs>
